--- a/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 17,41</t>
+          <t>-1,74; 17,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 1,65</t>
+          <t>-17,62; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 15,37</t>
+          <t>-5,73; 14,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 7,45</t>
+          <t>-29,36; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 143,0</t>
+          <t>-9,43; 131,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 10,25</t>
+          <t>-63,07; 9,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 102,99</t>
+          <t>-24,71; 100,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 99,63</t>
+          <t>-87,73; 122,73</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 10,08</t>
+          <t>-11,92; 9,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 8,47</t>
+          <t>-11,4; 8,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 5,94</t>
+          <t>-12,59; 7,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 27,72</t>
+          <t>-27,95; 26,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 56,34</t>
+          <t>-40,55; 46,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 51,54</t>
+          <t>-42,23; 45,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 32,31</t>
+          <t>-44,7; 39,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 13,07</t>
+          <t>-8,25; 15,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 13,18</t>
+          <t>-5,38; 13,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 9,73</t>
+          <t>-14,14; 10,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 24,29</t>
+          <t>-42,8; 33,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 82,11</t>
+          <t>-34,54; 97,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 166,23</t>
+          <t>-33,63; 151,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 59,39</t>
+          <t>-53,05; 67,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 281,03</t>
+          <t>-100,0; 358,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 11,48</t>
+          <t>-2,5; 11,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,9</t>
+          <t>-6,85; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,93</t>
+          <t>-4,64; 6,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 16,69</t>
+          <t>-14,84; 17,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 62,66</t>
+          <t>-10,07; 67,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 41,14</t>
+          <t>-26,17; 39,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 54,02</t>
+          <t>-24,11; 47,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,06; 131,93</t>
+          <t>-58,38; 129,72</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 16,88</t>
+          <t>-1,22; 17,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 14,67</t>
+          <t>-1,11; 14,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 6,64</t>
+          <t>-9,24; 6,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 29,72</t>
+          <t>-8,35; 30,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 154,81</t>
+          <t>-8,51; 145,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 140,92</t>
+          <t>-6,75; 133,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 47,33</t>
+          <t>-42,88; 42,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 340,15</t>
+          <t>-46,57; 377,45</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 14,04</t>
+          <t>-7,51; 13,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 21,07</t>
+          <t>-5,55; 20,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 14,05</t>
+          <t>-11,53; 13,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 28,18</t>
+          <t>-23,2; 31,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 110,85</t>
+          <t>-34,89; 115,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 160,55</t>
+          <t>-21,25; 147,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 85,51</t>
+          <t>-40,34; 79,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 8,15</t>
+          <t>0,53; 8,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,64</t>
+          <t>-2,56; 5,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,59</t>
+          <t>-3,58; 3,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 8,13</t>
+          <t>-9,04; 7,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 45,51</t>
+          <t>2,47; 47,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 31,46</t>
+          <t>-11,8; 28,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 20,08</t>
+          <t>-16,82; 19,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 53,39</t>
+          <t>-40,34; 49,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 17,1</t>
+          <t>-2,34; 17,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 1,26</t>
+          <t>-17,59; 2,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 14,95</t>
+          <t>-5,34; 15,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 7,09</t>
+          <t>-29,58; 7,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 131,85</t>
+          <t>-10,27; 130,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 9,86</t>
+          <t>-63,43; 14,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 100,42</t>
+          <t>-22,8; 95,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 122,73</t>
+          <t>-87,26; 100,26</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 9,06</t>
+          <t>-11,87; 10,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 8,13</t>
+          <t>-10,94; 8,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 7,08</t>
+          <t>-12,67; 6,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 26,92</t>
+          <t>-25,82; 28,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 46,59</t>
+          <t>-37,36; 54,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 45,99</t>
+          <t>-42,23; 49,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 39,91</t>
+          <t>-45,27; 40,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 15,0</t>
+          <t>-8,38; 13,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 13,0</t>
+          <t>-4,95; 13,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 10,55</t>
+          <t>-14,48; 9,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 33,22</t>
+          <t>-44,66; 40,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 97,46</t>
+          <t>-34,27; 87,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 151,36</t>
+          <t>-31,24; 140,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 67,67</t>
+          <t>-52,68; 61,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 358,65</t>
+          <t>-100,0; 398,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 11,97</t>
+          <t>-2,23; 11,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 7,25</t>
+          <t>-5,74; 8,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,53</t>
+          <t>-4,88; 7,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 17,25</t>
+          <t>-12,2; 16,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 67,49</t>
+          <t>-9,52; 62,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 39,86</t>
+          <t>-22,1; 48,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 47,96</t>
+          <t>-24,8; 55,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 129,72</t>
+          <t>-52,3; 119,26</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 17,08</t>
+          <t>-1,51; 16,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 14,56</t>
+          <t>-0,63; 14,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 6,13</t>
+          <t>-8,89; 6,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 30,12</t>
+          <t>-7,79; 27,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 145,5</t>
+          <t>-7,36; 159,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 133,21</t>
+          <t>-6,47; 129,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 42,97</t>
+          <t>-40,82; 49,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 377,45</t>
+          <t>-52,15; 293,94</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 13,89</t>
+          <t>-7,49; 13,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 20,03</t>
+          <t>-4,65; 21,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 13,21</t>
+          <t>-12,98; 13,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 31,71</t>
+          <t>-21,81; 30,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 115,74</t>
+          <t>-32,08; 109,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 147,29</t>
+          <t>-20,13; 155,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 79,48</t>
+          <t>-44,34; 80,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 8,64</t>
+          <t>0,31; 8,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,04</t>
+          <t>-2,22; 5,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,45</t>
+          <t>-3,53; 3,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,53</t>
+          <t>-9,14; 8,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 47,81</t>
+          <t>1,48; 45,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 28,88</t>
+          <t>-10,36; 28,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 19,4</t>
+          <t>-16,94; 20,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 49,71</t>
+          <t>-40,28; 52,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-9,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,03%</t>
+          <t>-43,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 17,27</t>
+          <t>-0,93; 17,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 2,43</t>
+          <t>-18,03; 1,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 15,67</t>
+          <t>-5,35; 15,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 7,68</t>
+          <t>-30,65; 7,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 130,72</t>
+          <t>-6,78; 143,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 14,39</t>
+          <t>-65,3; 10,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 95,79</t>
+          <t>-21,62; 102,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 100,26</t>
+          <t>-86,19; 104,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 10,28</t>
+          <t>-11,38; 10,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 8,38</t>
+          <t>-11,09; 8,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 6,74</t>
+          <t>-12,01; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 28,36</t>
+          <t>-26,33; 27,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 54,9</t>
+          <t>-38,14; 56,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 49,85</t>
+          <t>-40,87; 51,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 40,43</t>
+          <t>-43,37; 32,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,57</t>
+          <t>-16,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,64%</t>
+          <t>-55,14%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 13,54</t>
+          <t>-8,24; 13,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 13,39</t>
+          <t>-4,98; 13,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 9,4</t>
+          <t>-13,91; 9,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 40,65</t>
+          <t>-48,92; 19,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 87,36</t>
+          <t>-34,11; 82,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 140,53</t>
+          <t>-32,28; 166,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 61,27</t>
+          <t>-52,47; 59,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 398,99</t>
+          <t>-100,0; 196,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 11,68</t>
+          <t>-3,08; 11,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,74</t>
+          <t>-5,9; 7,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 7,13</t>
+          <t>-5,58; 6,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 16,19</t>
+          <t>-12,29; 19,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 62,66</t>
+          <t>-12,08; 62,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 48,96</t>
+          <t>-23,17; 41,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 55,72</t>
+          <t>-28,12; 54,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 119,26</t>
+          <t>-48,87; 161,96</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 16,95</t>
+          <t>-1,77; 16,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 14,32</t>
+          <t>-0,74; 14,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 6,99</t>
+          <t>-9,14; 6,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 27,42</t>
+          <t>-8,5; 31,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 159,7</t>
+          <t>-10,3; 154,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 129,6</t>
+          <t>-4,89; 140,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 49,48</t>
+          <t>-41,99; 47,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 293,94</t>
+          <t>-51,03; 363,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 13,47</t>
+          <t>-8,14; 14,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 21,6</t>
+          <t>-4,3; 21,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 13,43</t>
+          <t>-11,49; 14,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 30,3</t>
+          <t>-23,73; 27,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 109,19</t>
+          <t>-36,73; 110,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 155,52</t>
+          <t>-18,65; 160,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 80,72</t>
+          <t>-40,23; 85,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-4,69%</t>
+          <t>-0,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,06</t>
+          <t>0,32; 8,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 5,11</t>
+          <t>-2,03; 5,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,67</t>
+          <t>-3,75; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 8,22</t>
+          <t>-8,63; 9,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 45,09</t>
+          <t>1,44; 45,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 28,89</t>
+          <t>-9,93; 31,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 20,29</t>
+          <t>-17,72; 20,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 52,91</t>
+          <t>-37,83; 62,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-8,09</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-35,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-43,99%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.758825166135288</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-8.094518936223565</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.778854915255759</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-9.432556607396904</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4432817730681275</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3580064227090695</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2422235368077081</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.4399295578168563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,93; 17,41</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,03; 1,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 15,37</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-30,65; 7,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-6,78; 143,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-65,3; 10,25</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-21,62; 102,99</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-86,19; 104,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.9319156934910203</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.02902798068033</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.347264530206071</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-30.64962856269657</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.06782614088176994</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6529696756099451</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2162293139247946</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8619104012839138</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>17.41359040329367</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.645380963843995</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15.36750751840559</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.970404061460451</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.430018202340016</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1024943338849778</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.029880025600761</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.048519137799481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,96</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-12,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,38; 10,08</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-11,09; 8,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-12,01; 5,94</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-26,33; 27,47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-38,14; 56,34</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-40,87; 51,54</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 32,31</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.9406204974147181</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.501362746531898</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.960730348547791</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.8300977593515474</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.03813238869156858</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06746640217572736</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1273207180481451</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.0430514533319593</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-16,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-10,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-55,14%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11.38201331787716</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-11.09489260996883</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-12.00652690034593</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-26.33312419231781</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3813747309177739</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4087176636758399</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4337253825049111</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; 13,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 13,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,91; 9,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-48,92; 19,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-34,11; 82,11</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-32,28; 166,23</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-52,47; 59,39</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 196,79</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.08477890041182</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.468876053962743</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.935891804441355</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>27.46690154758179</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5634205944394663</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5154025638079893</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3231273285130913</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +815,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.224053493174163</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.249777829391133</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.325772677274895</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-16.82073496525186</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1104722195173642</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.329403094678429</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1057544901927431</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5513778557373111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 11,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,9; 7,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,58; 6,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-12,29; 19,62</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-12,08; 62,66</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-23,17; 41,14</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-28,12; 54,02</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-48,87; 161,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.235442845520627</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.978196198106929</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.90889495083837</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-48.92375005899057</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3411107866980414</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3228467727482795</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5247123134024743</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.07213686707525</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.18093411473233</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.732462216299055</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.72472716584968</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8211128816567153</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.662345691802156</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5938752407930283</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.967928417892996</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,63</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,77</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,69%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-7,36%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 16,88</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 14,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-9,14; 6,64</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-8,5; 31,59</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-10,3; 154,81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,89; 140,92</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-41,99; 47,33</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-51,03; 363,53</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>4.000020830370768</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9836774306676038</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.182662892387318</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.394891090930757</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1816587627825992</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.04448473047024582</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07243591716823744</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1708269674778338</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.083799090255775</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.897595529159109</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.575596505986501</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-12.286329012393</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1208238062209765</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2316764072561672</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2812238326492727</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4887478280231329</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-8,14; 14,04</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 21,07</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-11,49; 14,05</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-23,73; 27,1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-36,73; 110,85</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-18,65; 160,55</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-40,23; 85,51</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.48013328827356</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.900594628475218</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.926122335667549</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>19.6209267569411</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6265908875923386</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4114459608216241</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5402043424752666</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.61959166910783</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1015,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-0,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.632703979875327</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>6.766876738455774</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.329584818158178</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>8.381083299302391</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.5068936705089147</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4629889057892977</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.07363350602617756</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.5881919542832987</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 8,15</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,03; 5,64</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 3,59</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-8,63; 9,37</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 45,51</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-9,93; 31,46</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-17,72; 20,08</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-37,83; 62,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.765970283480919</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7377091049321628</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.138168310322893</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.504268860897517</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1030361709458128</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04891522954115254</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.419856137825603</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5102612198026133</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>16.87509647560556</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>14.67028651284158</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.641832859740307</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>31.59009397024873</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.54813697389235</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.409224629388673</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4732947868381335</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.635302697980568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.654998314900092</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8.259039426891016</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.8792126826716901</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1.472308925585428</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1483902625864879</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.4421736570153464</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.03845910596825539</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.106978704665548</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-8.135464804731267</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-4.303965091681648</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-11.49138287788786</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-23.72913428940124</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3672983731982823</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1865171954859274</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.4023104288637749</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>14.04367965130385</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>21.06832763581148</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>14.04673818056514</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>27.09563802602688</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.108476530853967</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.605478392567319</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.8550774425225441</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>4.235885173935205</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.618665321325508</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.05280288343085526</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.05819954979845443</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2143819718365484</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.08414603820309581</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.002711468733181467</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.00304727702740817</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.3233078290563985</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.025809382393985</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.747684160502526</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.625359208182557</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0.01441591003978587</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.09928873148666317</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1771576836477235</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3783479097917323</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8.145705667477552</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>5.63710462073898</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.593562295307435</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>9.37101183651829</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.4550632346400872</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.3145872628857212</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.200796108124905</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.6282442204725087</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1309,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
